--- a/data/processed/stock analysis 2021-2024 KLCI 30 index.xlsx
+++ b/data/processed/stock analysis 2021-2024 KLCI 30 index.xlsx
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.48</v>
+        <v>4.29</v>
       </c>
       <c r="C2" t="n">
-        <v>548</v>
+        <v>429</v>
       </c>
       <c r="D2" t="n">
+        <v>0.0598</v>
+      </c>
+      <c r="E2" t="n">
         <v>0.09429999999999999</v>
       </c>
-      <c r="E2" t="n">
-        <v>0.1002</v>
-      </c>
       <c r="F2" t="n">
-        <v>0.7966</v>
+        <v>0.4806</v>
       </c>
     </row>
     <row r="3">
@@ -489,19 +489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.49</v>
+        <v>2.61</v>
       </c>
       <c r="C3" t="n">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0587</v>
+        <v>-0.0626</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1142</v>
+        <v>0.1143</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6407</v>
+        <v>-0.674</v>
       </c>
     </row>
     <row r="4">
@@ -511,19 +511,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.62</v>
+        <v>3.68</v>
       </c>
       <c r="C4" t="n">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0045</v>
+        <v>-0.0015</v>
       </c>
       <c r="E4" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.1112</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1997</v>
+        <v>-0.1437</v>
       </c>
     </row>
     <row r="5">
@@ -533,19 +533,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="C5" t="n">
-        <v>820</v>
+        <v>680</v>
       </c>
       <c r="D5" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.057</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0835</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8041</v>
+        <v>0.615</v>
       </c>
     </row>
     <row r="6">
@@ -555,19 +555,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.74</v>
+        <v>6.58</v>
       </c>
       <c r="C6" t="n">
-        <v>474</v>
+        <v>658</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1383</v>
+        <v>0.1947</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3223</v>
+        <v>0.1316</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3844</v>
+        <v>1.3693</v>
       </c>
     </row>
     <row r="7">
@@ -577,19 +577,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20.56</v>
+        <v>19.2</v>
       </c>
       <c r="C7" t="n">
-        <v>2056</v>
+        <v>1920</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0108</v>
+        <v>-0.0011</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0516</v>
+        <v>0.0489</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.07049999999999999</v>
+        <v>-0.3184</v>
       </c>
     </row>
     <row r="8">
@@ -599,19 +599,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.3</v>
+        <v>6.3</v>
       </c>
       <c r="C8" t="n">
-        <v>730</v>
+        <v>630</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0232</v>
+        <v>-0.004</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0764</v>
+        <v>0.0423</v>
       </c>
       <c r="F8" t="n">
-        <v>0.114</v>
+        <v>-0.4352</v>
       </c>
     </row>
     <row r="9">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.88</v>
+        <v>3.7</v>
       </c>
       <c r="C9" t="n">
-        <v>388</v>
+        <v>370</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0055</v>
+        <v>-0.0026</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0614</v>
+        <v>0.0746</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1462</v>
+        <v>-0.2287</v>
       </c>
     </row>
     <row r="10">
@@ -643,19 +643,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21.8</v>
+        <v>20.64</v>
       </c>
       <c r="C10" t="n">
-        <v>2180</v>
+        <v>2064</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0027</v>
+        <v>-0.0075</v>
       </c>
       <c r="E10" t="n">
-        <v>0.054</v>
+        <v>0.0625</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2169</v>
+        <v>-0.3516</v>
       </c>
     </row>
     <row r="11">
@@ -665,19 +665,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10.24</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>1024</v>
+        <v>996</v>
       </c>
       <c r="D11" t="n">
-        <v>0.037</v>
+        <v>0.0384</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0437</v>
+        <v>0.0366</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5165999999999999</v>
+        <v>0.6554</v>
       </c>
     </row>
     <row r="12">
@@ -687,19 +687,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.65</v>
+        <v>3.53</v>
       </c>
       <c r="C12" t="n">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0216</v>
+        <v>-0.0327</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0789</v>
+        <v>0.0828</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.457</v>
+        <v>-0.5699</v>
       </c>
     </row>
     <row r="13">
@@ -709,19 +709,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7.6</v>
+        <v>8.52</v>
       </c>
       <c r="C13" t="n">
-        <v>760</v>
+        <v>852</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0194</v>
+        <v>0.043</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1065</v>
+        <v>0.0677</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0462</v>
+        <v>0.4209</v>
       </c>
     </row>
     <row r="14">
@@ -731,19 +731,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="C14" t="n">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0673</v>
+        <v>-0.0801</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3083</v>
+        <v>0.2953</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.265</v>
+        <v>-0.3202</v>
       </c>
     </row>
     <row r="15">
@@ -753,19 +753,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>99.98</v>
+        <v>121.5</v>
       </c>
       <c r="C15" t="n">
-        <v>9998</v>
+        <v>12150</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0439</v>
+        <v>-0.0153</v>
       </c>
       <c r="E15" t="n">
-        <v>0.055</v>
+        <v>0.0529</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0612</v>
+        <v>-0.5610000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -775,19 +775,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.17</v>
+        <v>6.31</v>
       </c>
       <c r="C16" t="n">
-        <v>517</v>
+        <v>631</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0844</v>
+        <v>-0.0645</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0663</v>
+        <v>0.0636</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4914</v>
+        <v>-1.2405</v>
       </c>
     </row>
     <row r="17">
@@ -797,19 +797,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19.32</v>
+        <v>17.44</v>
       </c>
       <c r="C17" t="n">
-        <v>1932</v>
+        <v>1744</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0051</v>
+        <v>-0.0144</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1172</v>
+        <v>0.1273</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0794</v>
+        <v>-0.227</v>
       </c>
     </row>
     <row r="18">
@@ -819,19 +819,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17.68</v>
+        <v>17.82</v>
       </c>
       <c r="C18" t="n">
-        <v>1768</v>
+        <v>1782</v>
       </c>
       <c r="D18" t="n">
-        <v>0.007</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0259</v>
+        <v>0.0206</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2858</v>
+        <v>-0.2217</v>
       </c>
     </row>
     <row r="19">
@@ -841,19 +841,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>12.4</v>
+        <v>14.3</v>
       </c>
       <c r="C19" t="n">
-        <v>1240</v>
+        <v>1430</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0362</v>
+        <v>-0.018</v>
       </c>
       <c r="E19" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5215</v>
+        <v>-0.4002</v>
       </c>
     </row>
     <row r="20">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.9</v>
+        <v>5.76</v>
       </c>
       <c r="C20" t="n">
-        <v>490</v>
+        <v>576</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0311</v>
+        <v>-0.0033</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1198</v>
+        <v>0.1576</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3803</v>
+        <v>-0.1126</v>
       </c>
     </row>
     <row r="21">
@@ -885,19 +885,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4.56</v>
+        <v>4.02</v>
       </c>
       <c r="C21" t="n">
-        <v>456</v>
+        <v>402</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0157</v>
+        <v>-0.0064</v>
       </c>
       <c r="E21" t="n">
-        <v>0.07489999999999999</v>
+        <v>0.0834</v>
       </c>
       <c r="F21" t="n">
-        <v>0.017</v>
+        <v>-0.2502</v>
       </c>
     </row>
     <row r="22">
@@ -907,19 +907,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4.76</v>
+        <v>6.52</v>
       </c>
       <c r="C22" t="n">
-        <v>476</v>
+        <v>652</v>
       </c>
       <c r="D22" t="n">
-        <v>0.005</v>
+        <v>0.0579</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1601</v>
+        <v>0.0736</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0593</v>
+        <v>0.5908</v>
       </c>
     </row>
     <row r="23">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6.48</v>
+        <v>5.51</v>
       </c>
       <c r="C23" t="n">
-        <v>648</v>
+        <v>551</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0273</v>
+        <v>-0.0014</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0604</v>
+        <v>0.0332</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2124</v>
+        <v>-0.4765</v>
       </c>
     </row>
     <row r="24">
@@ -951,19 +951,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4.95</v>
+        <v>4.22</v>
       </c>
       <c r="C24" t="n">
-        <v>495</v>
+        <v>422</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0615</v>
+        <v>0.041</v>
       </c>
       <c r="E24" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.1144</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4822</v>
+        <v>0.2325</v>
       </c>
     </row>
     <row r="25">
@@ -973,19 +973,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="C25" t="n">
-        <v>236</v>
+        <v>262</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0186</v>
+        <v>0.0424</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0844</v>
+        <v>0.0732</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0492</v>
+        <v>0.3825</v>
       </c>
     </row>
     <row r="26">
@@ -995,19 +995,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.79</v>
+        <v>3.61</v>
       </c>
       <c r="C26" t="n">
-        <v>479</v>
+        <v>361</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2112</v>
+        <v>0.1793</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2715</v>
+        <v>0.2351</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7246</v>
+        <v>0.7013</v>
       </c>
     </row>
     <row r="27">
@@ -1017,19 +1017,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.65</v>
+        <v>6.76</v>
       </c>
       <c r="C27" t="n">
-        <v>665</v>
+        <v>676</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0519</v>
+        <v>0.0643</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1151</v>
+        <v>0.1098</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3251</v>
+        <v>0.4542</v>
       </c>
     </row>
     <row r="28">
@@ -1039,19 +1039,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>14.94</v>
+        <v>13.78</v>
       </c>
       <c r="C28" t="n">
-        <v>1494</v>
+        <v>1378</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0921</v>
+        <v>0.0927</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1374</v>
+        <v>0.1431</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5648</v>
+        <v>0.5468</v>
       </c>
     </row>
     <row r="29">
@@ -1061,19 +1061,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.67</v>
+        <v>3.45</v>
       </c>
       <c r="C29" t="n">
-        <v>267</v>
+        <v>345</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3882</v>
+        <v>0.5127</v>
       </c>
       <c r="E29" t="n">
-        <v>0.5476</v>
+        <v>0.5143</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6826</v>
+        <v>0.9687</v>
       </c>
     </row>
     <row r="30">
@@ -1083,19 +1083,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4.42</v>
+        <v>4.82</v>
       </c>
       <c r="C30" t="n">
-        <v>442</v>
+        <v>482</v>
       </c>
       <c r="D30" t="n">
-        <v>0.5216</v>
+        <v>0.644</v>
       </c>
       <c r="E30" t="n">
-        <v>0.8035</v>
+        <v>0.8361</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6312</v>
+        <v>0.753</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/stock analysis 2021-2024 KLCI 30 index.xlsx
+++ b/data/processed/stock analysis 2021-2024 KLCI 30 index.xlsx
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.29</v>
+        <v>5.48</v>
       </c>
       <c r="C2" t="n">
-        <v>429</v>
+        <v>548</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0598</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.1002</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4806</v>
+        <v>0.7966</v>
       </c>
     </row>
     <row r="3">
@@ -489,19 +489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.61</v>
+        <v>2.49</v>
       </c>
       <c r="C3" t="n">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0626</v>
+        <v>-0.0587</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1143</v>
+        <v>0.1142</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.674</v>
+        <v>-0.6407</v>
       </c>
     </row>
     <row r="4">
@@ -511,19 +511,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.68</v>
+        <v>3.62</v>
       </c>
       <c r="C4" t="n">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0015</v>
+        <v>-0.0045</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1112</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1437</v>
+        <v>-0.1997</v>
       </c>
     </row>
     <row r="5">
@@ -533,19 +533,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>680</v>
+        <v>820</v>
       </c>
       <c r="D5" t="n">
-        <v>0.057</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.0835</v>
       </c>
       <c r="F5" t="n">
-        <v>0.615</v>
+        <v>0.8041</v>
       </c>
     </row>
     <row r="6">
@@ -555,19 +555,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.58</v>
+        <v>4.74</v>
       </c>
       <c r="C6" t="n">
-        <v>658</v>
+        <v>474</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1947</v>
+        <v>0.1383</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1316</v>
+        <v>0.3223</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3693</v>
+        <v>0.3844</v>
       </c>
     </row>
     <row r="7">
@@ -577,19 +577,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19.2</v>
+        <v>20.56</v>
       </c>
       <c r="C7" t="n">
-        <v>1920</v>
+        <v>2056</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0011</v>
+        <v>0.0108</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0489</v>
+        <v>0.0516</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3184</v>
+        <v>-0.07049999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -599,19 +599,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.3</v>
+        <v>7.3</v>
       </c>
       <c r="C8" t="n">
-        <v>630</v>
+        <v>730</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.004</v>
+        <v>0.0232</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0423</v>
+        <v>0.0764</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4352</v>
+        <v>0.114</v>
       </c>
     </row>
     <row r="9">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.7</v>
+        <v>3.88</v>
       </c>
       <c r="C9" t="n">
-        <v>370</v>
+        <v>388</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0026</v>
+        <v>0.0055</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0746</v>
+        <v>0.0614</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2287</v>
+        <v>-0.1462</v>
       </c>
     </row>
     <row r="10">
@@ -643,19 +643,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20.64</v>
+        <v>21.8</v>
       </c>
       <c r="C10" t="n">
-        <v>2064</v>
+        <v>2180</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0075</v>
+        <v>0.0027</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0625</v>
+        <v>0.054</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3516</v>
+        <v>-0.2169</v>
       </c>
     </row>
     <row r="11">
@@ -665,19 +665,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9.960000000000001</v>
+        <v>10.24</v>
       </c>
       <c r="C11" t="n">
-        <v>996</v>
+        <v>1024</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0384</v>
+        <v>0.037</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0366</v>
+        <v>0.0437</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6554</v>
+        <v>0.5165999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -687,19 +687,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.53</v>
+        <v>3.65</v>
       </c>
       <c r="C12" t="n">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0327</v>
+        <v>-0.0216</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0828</v>
+        <v>0.0789</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5699</v>
+        <v>-0.457</v>
       </c>
     </row>
     <row r="13">
@@ -709,19 +709,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8.52</v>
+        <v>7.6</v>
       </c>
       <c r="C13" t="n">
-        <v>852</v>
+        <v>760</v>
       </c>
       <c r="D13" t="n">
-        <v>0.043</v>
+        <v>0.0194</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0677</v>
+        <v>0.1065</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4209</v>
+        <v>0.0462</v>
       </c>
     </row>
     <row r="14">
@@ -731,19 +731,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="C14" t="n">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0801</v>
+        <v>-0.0673</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2953</v>
+        <v>0.3083</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3202</v>
+        <v>-0.265</v>
       </c>
     </row>
     <row r="15">
@@ -753,19 +753,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>121.5</v>
+        <v>99.98</v>
       </c>
       <c r="C15" t="n">
-        <v>12150</v>
+        <v>9998</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0153</v>
+        <v>-0.0439</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0529</v>
+        <v>0.055</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-1.0612</v>
       </c>
     </row>
     <row r="16">
@@ -775,19 +775,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6.31</v>
+        <v>5.17</v>
       </c>
       <c r="C16" t="n">
-        <v>631</v>
+        <v>517</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0645</v>
+        <v>-0.0844</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0636</v>
+        <v>0.0663</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2405</v>
+        <v>-1.4914</v>
       </c>
     </row>
     <row r="17">
@@ -797,19 +797,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17.44</v>
+        <v>19.32</v>
       </c>
       <c r="C17" t="n">
-        <v>1744</v>
+        <v>1932</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0144</v>
+        <v>0.0051</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1273</v>
+        <v>0.1172</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.227</v>
+        <v>-0.0794</v>
       </c>
     </row>
     <row r="18">
@@ -819,19 +819,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17.82</v>
+        <v>17.68</v>
       </c>
       <c r="C18" t="n">
-        <v>1782</v>
+        <v>1768</v>
       </c>
       <c r="D18" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.007</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0206</v>
+        <v>0.0259</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2217</v>
+        <v>-0.2858</v>
       </c>
     </row>
     <row r="19">
@@ -841,19 +841,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14.3</v>
+        <v>12.4</v>
       </c>
       <c r="C19" t="n">
-        <v>1430</v>
+        <v>1240</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.018</v>
+        <v>-0.0362</v>
       </c>
       <c r="E19" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4002</v>
+        <v>-0.5215</v>
       </c>
     </row>
     <row r="20">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.76</v>
+        <v>4.9</v>
       </c>
       <c r="C20" t="n">
-        <v>576</v>
+        <v>490</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0033</v>
+        <v>-0.0311</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1576</v>
+        <v>0.1198</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1126</v>
+        <v>-0.3803</v>
       </c>
     </row>
     <row r="21">
@@ -885,19 +885,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4.02</v>
+        <v>4.56</v>
       </c>
       <c r="C21" t="n">
-        <v>402</v>
+        <v>456</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0064</v>
+        <v>0.0157</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0834</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2502</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="22">
@@ -907,19 +907,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6.52</v>
+        <v>4.76</v>
       </c>
       <c r="C22" t="n">
-        <v>652</v>
+        <v>476</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0579</v>
+        <v>0.005</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0736</v>
+        <v>0.1601</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5908</v>
+        <v>-0.0593</v>
       </c>
     </row>
     <row r="23">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5.51</v>
+        <v>6.48</v>
       </c>
       <c r="C23" t="n">
-        <v>551</v>
+        <v>648</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0014</v>
+        <v>0.0273</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0332</v>
+        <v>0.0604</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4765</v>
+        <v>0.2124</v>
       </c>
     </row>
     <row r="24">
@@ -951,19 +951,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4.22</v>
+        <v>4.95</v>
       </c>
       <c r="C24" t="n">
-        <v>422</v>
+        <v>495</v>
       </c>
       <c r="D24" t="n">
-        <v>0.041</v>
+        <v>0.0615</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1144</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2325</v>
+        <v>0.4822</v>
       </c>
     </row>
     <row r="25">
@@ -973,19 +973,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="C25" t="n">
-        <v>262</v>
+        <v>236</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0424</v>
+        <v>0.0186</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0732</v>
+        <v>0.0844</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3825</v>
+        <v>0.0492</v>
       </c>
     </row>
     <row r="26">
@@ -995,19 +995,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.61</v>
+        <v>4.79</v>
       </c>
       <c r="C26" t="n">
-        <v>361</v>
+        <v>479</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1793</v>
+        <v>0.2112</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2351</v>
+        <v>0.2715</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7013</v>
+        <v>0.7246</v>
       </c>
     </row>
     <row r="27">
@@ -1017,19 +1017,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.76</v>
+        <v>6.65</v>
       </c>
       <c r="C27" t="n">
-        <v>676</v>
+        <v>665</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0643</v>
+        <v>0.0519</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1098</v>
+        <v>0.1151</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4542</v>
+        <v>0.3251</v>
       </c>
     </row>
     <row r="28">
@@ -1039,19 +1039,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>13.78</v>
+        <v>14.94</v>
       </c>
       <c r="C28" t="n">
-        <v>1378</v>
+        <v>1494</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0927</v>
+        <v>0.0921</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1431</v>
+        <v>0.1374</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5468</v>
+        <v>0.5648</v>
       </c>
     </row>
     <row r="29">
@@ -1061,19 +1061,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3.45</v>
+        <v>2.67</v>
       </c>
       <c r="C29" t="n">
-        <v>345</v>
+        <v>267</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5127</v>
+        <v>0.3882</v>
       </c>
       <c r="E29" t="n">
-        <v>0.5143</v>
+        <v>0.5476</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9687</v>
+        <v>0.6826</v>
       </c>
     </row>
     <row r="30">
@@ -1083,19 +1083,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4.82</v>
+        <v>4.42</v>
       </c>
       <c r="C30" t="n">
-        <v>482</v>
+        <v>442</v>
       </c>
       <c r="D30" t="n">
-        <v>0.644</v>
+        <v>0.5216</v>
       </c>
       <c r="E30" t="n">
-        <v>0.8361</v>
+        <v>0.8035</v>
       </c>
       <c r="F30" t="n">
-        <v>0.753</v>
+        <v>0.6312</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/stock analysis 2021-2024 KLCI 30 index.xlsx
+++ b/data/processed/stock analysis 2021-2024 KLCI 30 index.xlsx
@@ -561,13 +561,13 @@
         <v>474</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1383</v>
+        <v>0.2579</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3223</v>
+        <v>0.1694</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3844</v>
+        <v>1.4372</v>
       </c>
     </row>
     <row r="7">
@@ -797,19 +797,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19.32</v>
+        <v>19.1041</v>
       </c>
       <c r="C17" t="n">
-        <v>1932</v>
+        <v>1910.41</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0051</v>
+        <v>0.0063</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1172</v>
+        <v>0.1178</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0794</v>
+        <v>-0.06909999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.36</v>
+        <v>2.3489</v>
       </c>
       <c r="C25" t="n">
-        <v>236</v>
+        <v>234.89</v>
       </c>
       <c r="D25" t="n">
         <v>0.0186</v>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.65</v>
+        <v>6.5904</v>
       </c>
       <c r="C27" t="n">
-        <v>665</v>
+        <v>659.04</v>
       </c>
       <c r="D27" t="n">
         <v>0.0519</v>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.67</v>
+        <v>2.5801</v>
       </c>
       <c r="C29" t="n">
-        <v>267</v>
+        <v>258.01</v>
       </c>
       <c r="D29" t="n">
         <v>0.3882</v>
@@ -1083,10 +1083,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4.42</v>
+        <v>4.2157</v>
       </c>
       <c r="C30" t="n">
-        <v>442</v>
+        <v>421.57</v>
       </c>
       <c r="D30" t="n">
         <v>0.5216</v>
